--- a/mi-proyecto/docs/TablasInventario.xlsx
+++ b/mi-proyecto/docs/TablasInventario.xlsx
@@ -376,7 +376,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -442,10 +442,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1387,7 +1383,7 @@
       </c>
       <c r="C2" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7853</v>
+        <v>2625</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>46219</v>
@@ -1412,7 +1408,7 @@
       </c>
       <c r="C3" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7278</v>
+        <v>5325</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>46220</v>
@@ -1438,7 +1434,7 @@
       </c>
       <c r="C4" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>1435</v>
+        <v>7740</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>46221</v>
@@ -1464,7 +1460,7 @@
       </c>
       <c r="C5" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>9187</v>
+        <v>7078</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>46222</v>
@@ -1490,7 +1486,7 @@
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7450</v>
+        <v>6571</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>46223</v>
@@ -1516,7 +1512,7 @@
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>4153</v>
+        <v>1513</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>46224</v>
@@ -1542,7 +1538,7 @@
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>1664</v>
+        <v>6311</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>46225</v>
@@ -1568,7 +1564,7 @@
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>1947</v>
+        <v>5738</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>46226</v>
@@ -1594,7 +1590,7 @@
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>3926</v>
+        <v>3163</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>46227</v>
@@ -1620,7 +1616,7 @@
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>6669</v>
+        <v>9652</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>46228</v>
@@ -1646,7 +1642,7 @@
       </c>
       <c r="C12" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>2229</v>
+        <v>5994</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>46229</v>
@@ -1672,7 +1668,7 @@
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>4977</v>
+        <v>4332</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>46230</v>
@@ -1698,7 +1694,7 @@
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>2811</v>
+        <v>5177</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>46231</v>
@@ -1724,7 +1720,7 @@
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>5443</v>
+        <v>7781</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>46232</v>
@@ -1750,7 +1746,7 @@
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>1698</v>
+        <v>1229</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>46233</v>
@@ -1774,7 +1770,7 @@
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>3611</v>
+        <v>2599</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>46234</v>
@@ -1798,7 +1794,7 @@
       </c>
       <c r="C18" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>2505</v>
+        <v>9278</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>46235</v>
@@ -1822,7 +1818,7 @@
       </c>
       <c r="C19" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>2872</v>
+        <v>9166</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>46236</v>
@@ -1846,7 +1842,7 @@
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>2520</v>
+        <v>7663</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>46237</v>
@@ -1871,7 +1867,7 @@
       </c>
       <c r="C21" s="8" t="n">
         <f aca="false">C3</f>
-        <v>7278</v>
+        <v>5325</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>46220</v>
@@ -1897,7 +1893,7 @@
       </c>
       <c r="C22" s="8" t="n">
         <f aca="false">C3</f>
-        <v>7278</v>
+        <v>5325</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>46220</v>
@@ -2631,7 +2627,7 @@
       <c r="B1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="7" t="s">
         <v>73</v>
       </c>
     </row>

--- a/mi-proyecto/docs/TablasInventario.xlsx
+++ b/mi-proyecto/docs/TablasInventario.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="91">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -214,13 +214,27 @@
     <t xml:space="preserve">Fecha de vencimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Cantidad entrada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precio de compra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEFO</t>
+    <t xml:space="preserve">Cantidad de inventario movido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor monetario del 
+Movimiento de inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motivo del movimento 
+De invetario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vencimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perdida</t>
   </si>
   <si>
     <t xml:space="preserve">Id cliente</t>
@@ -416,17 +430,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -457,8 +471,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -494,6 +508,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -740,78 +758,78 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -834,21 +852,21 @@
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="3.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="17.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="15.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="16.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="14.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="11.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="18.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="8.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="17.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="14" style="2" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1125" min="1024" style="2" width="7.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="17.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="14" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1125" min="1024" style="1" width="7.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1519,18 +1537,20 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="4.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="6.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="18.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="23.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="17.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1021" min="8" style="2" width="13.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1122" min="1022" style="2" width="7.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1020" min="9" style="1" width="13.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1121" min="1021" style="1" width="7.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
         <v>10</v>
       </c>
@@ -1549,10 +1569,10 @@
       <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="2" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1566,7 +1586,7 @@
       </c>
       <c r="C2" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>2659</v>
+        <v>4019</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>46219</v>
@@ -1578,7 +1598,10 @@
         <v>20</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>100000</v>
+        <v>-100000</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1591,7 +1614,7 @@
       </c>
       <c r="C3" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>3916</v>
+        <v>6463</v>
       </c>
       <c r="D3" s="12" t="n">
         <v>46220</v>
@@ -1603,7 +1626,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1400</v>
+        <v>-1400</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1617,7 +1640,7 @@
       </c>
       <c r="C4" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>1969</v>
+        <v>2851</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>46221</v>
@@ -1629,7 +1652,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>200</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1643,7 +1666,7 @@
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>6148</v>
+        <v>5086</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>46222</v>
@@ -1655,7 +1678,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>5000</v>
+        <v>-5000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1669,7 +1692,7 @@
       </c>
       <c r="C6" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>3670</v>
+        <v>1059</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>46223</v>
@@ -1681,7 +1704,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2500</v>
+        <v>-2500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1695,7 +1718,7 @@
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>6113</v>
+        <v>7621</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>46224</v>
@@ -1707,7 +1730,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>4500</v>
+        <v>-4500</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1721,7 +1744,7 @@
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>4018</v>
+        <v>6759</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>46225</v>
@@ -1733,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>8500</v>
+        <v>-8500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1747,7 +1770,7 @@
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>4255</v>
+        <v>5701</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>46226</v>
@@ -1759,7 +1782,7 @@
         <v>30</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>4000</v>
+        <v>-4000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1773,7 +1796,7 @@
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>8110</v>
+        <v>5496</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>46227</v>
@@ -1785,7 +1808,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>13500</v>
+        <v>-13500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1799,7 +1822,7 @@
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7391</v>
+        <v>1250</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>46228</v>
@@ -1811,7 +1834,7 @@
         <v>54</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>26000</v>
+        <v>-26000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1825,7 +1848,7 @@
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>5733</v>
+        <v>8274</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>46229</v>
@@ -1837,7 +1860,7 @@
         <v>10</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>3000</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1851,7 +1874,7 @@
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7476</v>
+        <v>4792</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>46230</v>
@@ -1863,7 +1886,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>25000</v>
+        <v>-25000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1877,7 +1900,7 @@
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>6202</v>
+        <v>9801</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>46231</v>
@@ -1889,7 +1912,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>75000</v>
+        <v>-75000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1903,7 +1926,7 @@
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7474</v>
+        <v>9047</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>46232</v>
@@ -1915,7 +1938,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>13000</v>
+        <v>-13000</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1929,7 +1955,7 @@
       </c>
       <c r="C16" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>1815</v>
+        <v>7427</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>46233</v>
@@ -1953,7 +1979,7 @@
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>8068</v>
+        <v>7137</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>46234</v>
@@ -1977,7 +2003,7 @@
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>8866</v>
+        <v>8105</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>46235</v>
@@ -2001,7 +2027,7 @@
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>9250</v>
+        <v>3558</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>46236</v>
@@ -2012,7 +2038,9 @@
       <c r="F19" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="5"/>
+      <c r="G19" s="5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
@@ -2025,7 +2053,7 @@
       </c>
       <c r="C20" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>2396</v>
+        <v>5102</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>46237</v>
@@ -2050,7 +2078,7 @@
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">C3</f>
-        <v>3916</v>
+        <v>6463</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>46220</v>
@@ -2063,7 +2091,10 @@
       </c>
       <c r="G21" s="5" t="n">
         <f aca="false">G3/F3*F21</f>
-        <v>-140</v>
+        <v>140</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2076,7 +2107,7 @@
       </c>
       <c r="C22" s="11" t="n">
         <f aca="false">C3</f>
-        <v>3916</v>
+        <v>6463</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>46220</v>
@@ -2089,6 +2120,9 @@
       </c>
       <c r="G22" s="5" t="n">
         <v>-3000</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2121,12 +2155,12 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="4.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="9.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="16.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="7" style="2" width="14.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1125" min="1025" style="2" width="7.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="9.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="14.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1125" min="1025" style="1" width="7.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2134,19 +2168,19 @@
         <v>10</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2166,7 +2200,7 @@
         <v>0.25</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2181,7 +2215,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2197,7 +2231,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2207,7 +2241,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2217,7 +2251,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2354,17 +2388,17 @@
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="12.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="15.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="5" style="2" width="9.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1125" min="1025" style="2" width="7.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="5" style="1" width="9.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1125" min="1025" style="1" width="7.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>55</v>
@@ -2373,7 +2407,7 @@
         <v>14</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2568,12 +2602,12 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="3.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="2" width="9.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="13.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="6" style="2" width="9.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1125" min="1025" style="2" width="7.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="9.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="6" style="1" width="9.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1125" min="1025" style="1" width="7.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2581,19 +2615,19 @@
         <v>10</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2601,13 +2635,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>10000000</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>3552277777</v>
@@ -2622,13 +2656,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>12555555</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>3225448454</v>
@@ -2799,30 +2833,30 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.04"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B3" s="7"/>
     </row>

--- a/mi-proyecto/docs/TablasInventario.xlsx
+++ b/mi-proyecto/docs/TablasInventario.xlsx
@@ -20,10 +20,10 @@
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">alertas!$A$1:$B$1</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">cliente!$A$1:$F$3</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'detalle de la venta'!$A$1:$D$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">lote!$A$1:$G$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">lote!$A$1:$H$22</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">producto!$B:$E</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">ventas!$A$1:$F$6</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm._FilterDatabase_1" vbProcedure="false">lote!$A$1:$G$20</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm._FilterDatabase_1" vbProcedure="false">lote!$A$1:$H$20</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fecha de registro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de expedición</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de vencimiento</t>
@@ -1534,23 +1537,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1020" min="9" style="1" width="13.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1121" min="1021" style="1" width="7.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="28.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1021" min="10" style="1" width="13.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1122" min="1022" style="1" width="7.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
         <v>10</v>
       </c>
@@ -1569,11 +1571,14 @@
       <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="10" t="s">
         <v>61</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1586,22 +1591,23 @@
       </c>
       <c r="C2" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>4019</v>
+        <v>6105</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>46219</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12" t="n">
         <v>46433</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="H2" s="5" t="n">
         <v>-100000</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>62</v>
+      <c r="I2" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1614,18 +1620,19 @@
       </c>
       <c r="C3" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>6463</v>
+        <v>3269</v>
       </c>
       <c r="D3" s="12" t="n">
         <v>46220</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12" t="n">
         <v>46428</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="H3" s="5" t="n">
         <v>-1400</v>
       </c>
     </row>
@@ -1640,18 +1647,19 @@
       </c>
       <c r="C4" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>2851</v>
+        <v>5188</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>46221</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="12"/>
+      <c r="F4" s="12" t="n">
         <v>46435</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="H4" s="13" t="n">
         <v>-200</v>
       </c>
     </row>
@@ -1666,18 +1674,19 @@
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>5086</v>
+        <v>2763</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>46222</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="n">
         <v>46436</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <v>-5000</v>
       </c>
     </row>
@@ -1692,18 +1701,19 @@
       </c>
       <c r="C6" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>1059</v>
+        <v>6205</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>46223</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="12"/>
+      <c r="F6" s="12" t="n">
         <v>46437</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <v>-2500</v>
       </c>
     </row>
@@ -1718,18 +1728,19 @@
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7621</v>
+        <v>1378</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>46224</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12" t="n">
         <v>46438</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>-4500</v>
       </c>
     </row>
@@ -1744,18 +1755,19 @@
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>6759</v>
+        <v>9259</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>46225</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="12"/>
+      <c r="F8" s="12" t="n">
         <v>46439</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <v>-8500</v>
       </c>
     </row>
@@ -1770,18 +1782,19 @@
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>5701</v>
+        <v>2689</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>46226</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="12"/>
+      <c r="F9" s="12" t="n">
         <v>46440</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <v>-4000</v>
       </c>
     </row>
@@ -1796,18 +1809,19 @@
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>5496</v>
+        <v>4706</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>46227</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="n">
         <v>46441</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>-13500</v>
       </c>
     </row>
@@ -1822,18 +1836,19 @@
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>1250</v>
+        <v>5581</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>46228</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="12"/>
+      <c r="F11" s="12" t="n">
         <v>46442</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <v>-26000</v>
       </c>
     </row>
@@ -1848,18 +1863,19 @@
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>8274</v>
+        <v>9485</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>46229</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="n">
         <v>46443</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>-3000</v>
       </c>
     </row>
@@ -1874,18 +1890,19 @@
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>4792</v>
+        <v>5711</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>46230</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="n">
         <v>46444</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13" s="5" t="n">
         <v>-25000</v>
       </c>
     </row>
@@ -1900,18 +1917,19 @@
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>9801</v>
+        <v>1744</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>46231</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="12"/>
+      <c r="F14" s="12" t="n">
         <v>46445</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>-75000</v>
       </c>
     </row>
@@ -1926,22 +1944,23 @@
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>9047</v>
+        <v>8302</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>46232</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="12"/>
+      <c r="F15" s="12" t="n">
         <v>46446</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>-13000</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>63</v>
+      <c r="I15" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1955,18 +1974,19 @@
       </c>
       <c r="C16" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7427</v>
+        <v>5198</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>46233</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="12"/>
+      <c r="F16" s="12" t="n">
         <v>46082</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
@@ -1979,18 +1999,19 @@
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>7137</v>
+        <v>1734</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>46234</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="12"/>
+      <c r="F17" s="12" t="n">
         <v>46448</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
@@ -2003,18 +2024,19 @@
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>8105</v>
+        <v>4047</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>46235</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="12"/>
+      <c r="F18" s="12" t="n">
         <v>46449</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
@@ -2027,18 +2049,19 @@
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>3558</v>
+        <v>6839</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>46236</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="12"/>
+      <c r="F19" s="12" t="n">
         <v>46450</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2053,18 +2076,19 @@
       </c>
       <c r="C20" s="11" t="n">
         <f aca="false">RANDBETWEEN(999,9999)</f>
-        <v>5102</v>
+        <v>5663</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>46237</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="12"/>
+      <c r="F20" s="12" t="n">
         <v>46247</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -2078,23 +2102,24 @@
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">C3</f>
-        <v>6463</v>
+        <v>3269</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>46220</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="12"/>
+      <c r="F21" s="12" t="n">
         <v>46428</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="6" t="n">
         <v>-2</v>
       </c>
-      <c r="G21" s="5" t="n">
-        <f aca="false">G3/F3*F21</f>
+      <c r="H21" s="5" t="n">
+        <f aca="false">H3/G3*G21</f>
         <v>140</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>64</v>
+      <c r="I21" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2107,22 +2132,23 @@
       </c>
       <c r="C22" s="11" t="n">
         <f aca="false">C3</f>
-        <v>6463</v>
+        <v>3269</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>46220</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="12"/>
+      <c r="F22" s="12" t="n">
         <v>46428</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="6" t="n">
         <v>-6</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>-3000</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>65</v>
+      <c r="I22" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2130,12 +2156,13 @@
       <c r="B23" s="7"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="7"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:H22"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="1.05208333333333" bottom="1.05208333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2168,19 +2195,19 @@
         <v>10</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2200,7 +2227,7 @@
         <v>0.25</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2215,7 +2242,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2231,7 +2258,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2241,7 +2268,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2251,7 +2278,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2398,7 +2425,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>55</v>
@@ -2407,7 +2434,7 @@
         <v>14</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2615,19 +2642,19 @@
         <v>10</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2635,13 +2662,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>10000000</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>3552277777</v>
@@ -2656,13 +2683,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>12555555</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>3225448454</v>
@@ -2839,24 +2866,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="7"/>
     </row>
